--- a/forms/trg/Formulir_TRG_renalnutrition.xlsx
+++ b/forms/trg/Formulir_TRG_renalnutrition.xlsx
@@ -686,7 +686,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Keahlian anggota banyak yang kosong. Mohon pilih keahlian utama untuk setiap anggota.</t>
+          <t>Data TRG ini relatif lengkap. Mohon periksa dan lengkapi mitra serta riset terbaik.</t>
         </is>
       </c>
     </row>
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="B24" s="7">
-        <f>COUNTA(Anggota!B5:B29)</f>
+        <f>COUNTA(Anggota!B5:B30)</f>
         <v/>
       </c>
     </row>
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="B25" s="7">
-        <f>COUNTA(Anggota!F5:F29)</f>
+        <f>COUNTA(Anggota!F5:F30)</f>
         <v/>
       </c>
     </row>
@@ -808,7 +808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M29"/>
+  <dimension ref="A1:M30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -913,22 +913,18 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>dr. Achmad Fikry, Sp.PD</t>
+          <t>Prof. Dr. dr. Haerani Rasyid, Sp.PD, KGH, Sp.GK (K), M.Kes</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
-        </is>
-      </c>
-      <c r="D5" s="11" t="inlineStr">
-        <is>
-          <t>Hasanuddin University</t>
-        </is>
-      </c>
+          <t>Leader</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="n"/>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>Internal Medicine | Nephrology | Rheumatology</t>
+          <t>Clinical Nutrition | Nephrology-Hypertension | Internal Medicine</t>
         </is>
       </c>
       <c r="F5" s="12" t="n"/>
@@ -936,10 +932,14 @@
       <c r="H5" s="12" t="n"/>
       <c r="I5" s="12" t="n"/>
       <c r="J5" s="12" t="n"/>
-      <c r="K5" s="12" t="n"/>
+      <c r="K5" s="11" t="inlineStr">
+        <is>
+          <t>6007114</t>
+        </is>
+      </c>
       <c r="L5" s="11" t="inlineStr">
         <is>
-          <t>57847748500</t>
+          <t>55749052100</t>
         </is>
       </c>
       <c r="M5" s="11" t="inlineStr">
@@ -954,12 +954,12 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>dr. St. Rabiul Zatalia, Sp.PD, KGH</t>
+          <t>dr. Achmad Fikry, Sp.PD</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="E6" s="11" t="inlineStr">
         <is>
-          <t>Internal medicine</t>
+          <t>Internal Medicine | Nephrology | Rheumatology</t>
         </is>
       </c>
       <c r="F6" s="12" t="n"/>
@@ -977,14 +977,10 @@
       <c r="H6" s="12" t="n"/>
       <c r="I6" s="12" t="n"/>
       <c r="J6" s="12" t="n"/>
-      <c r="K6" s="11" t="inlineStr">
-        <is>
-          <t>6869005</t>
-        </is>
-      </c>
+      <c r="K6" s="12" t="n"/>
       <c r="L6" s="11" t="inlineStr">
         <is>
-          <t>55986956200</t>
+          <t>57847748500</t>
         </is>
       </c>
       <c r="M6" s="11" t="inlineStr">
@@ -999,12 +995,12 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>Dr. dr. Andi Alfian Zainuddin, MKM</t>
+          <t>dr. St. Rabiul Zatalia, Sp.PD, KGH</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
@@ -1014,7 +1010,7 @@
       </c>
       <c r="E7" s="11" t="inlineStr">
         <is>
-          <t>Community medicine | Health management | environmental healt | hepidemiology</t>
+          <t>Internal medicine</t>
         </is>
       </c>
       <c r="F7" s="12" t="n"/>
@@ -1024,12 +1020,12 @@
       <c r="J7" s="12" t="n"/>
       <c r="K7" s="11" t="inlineStr">
         <is>
-          <t>6013409</t>
+          <t>6869005</t>
         </is>
       </c>
       <c r="L7" s="11" t="inlineStr">
         <is>
-          <t>57215695097</t>
+          <t>55986956200</t>
         </is>
       </c>
       <c r="M7" s="11" t="inlineStr">
@@ -1044,12 +1040,12 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>Prof. dr. Agussalim Bukhari, Sp.GK (K), Ph.D</t>
+          <t>Dr. dr. Andi Alfian Zainuddin, MKM</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
@@ -1059,7 +1055,7 @@
       </c>
       <c r="E8" s="11" t="inlineStr">
         <is>
-          <t>Insulin Resistance | Obesity | Molecular Biology | Clinical Nutrition | Immunology</t>
+          <t>Community medicine | Health management | environmental healt | hepidemiology</t>
         </is>
       </c>
       <c r="F8" s="12" t="n"/>
@@ -1069,12 +1065,12 @@
       <c r="J8" s="12" t="n"/>
       <c r="K8" s="11" t="inlineStr">
         <is>
-          <t>6043333</t>
+          <t>6013409</t>
         </is>
       </c>
       <c r="L8" s="11" t="inlineStr">
         <is>
-          <t>16024065100</t>
+          <t>57215695097</t>
         </is>
       </c>
       <c r="M8" s="11" t="inlineStr">
@@ -1089,18 +1085,22 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Prof. Shaw Watanabe</t>
+          <t>Prof. dr. Agussalim Bukhari, Sp.GK (K), Ph.D</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
-        </is>
-      </c>
-      <c r="D9" s="12" t="n"/>
+          <t>Lecturer</t>
+        </is>
+      </c>
+      <c r="D9" s="11" t="inlineStr">
+        <is>
+          <t>Hasanuddin University</t>
+        </is>
+      </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t>Japan Medical Rice Association</t>
+          <t>Insulin Resistance | Obesity | Molecular Biology | Clinical Nutrition | Immunology</t>
         </is>
       </c>
       <c r="F9" s="12" t="n"/>
@@ -1108,8 +1108,16 @@
       <c r="H9" s="12" t="n"/>
       <c r="I9" s="12" t="n"/>
       <c r="J9" s="12" t="n"/>
-      <c r="K9" s="12" t="n"/>
-      <c r="L9" s="12" t="n"/>
+      <c r="K9" s="11" t="inlineStr">
+        <is>
+          <t>6043333</t>
+        </is>
+      </c>
+      <c r="L9" s="11" t="inlineStr">
+        <is>
+          <t>16024065100</t>
+        </is>
+      </c>
       <c r="M9" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1122,20 +1130,20 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>Prof. Dr. dr. Haerani Rasyid, Sp.PD, KGH, Sp.GK (K), M.Kes</t>
+          <t>Prof. Shaw Watanabe</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
-        </is>
-      </c>
-      <c r="D10" s="11" t="inlineStr">
-        <is>
-          <t>Hasanuddin University</t>
-        </is>
-      </c>
-      <c r="E10" s="11" t="n"/>
+          <t>External collaborator</t>
+        </is>
+      </c>
+      <c r="D10" s="12" t="n"/>
+      <c r="E10" s="11" t="inlineStr">
+        <is>
+          <t>Japan Medical Rice Association</t>
+        </is>
+      </c>
       <c r="F10" s="12" t="n"/>
       <c r="G10" s="12" t="n"/>
       <c r="H10" s="12" t="n"/>
@@ -1155,12 +1163,12 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>Prof. dr. Agussalim Bukhari, Sp.GK (K), Ph.D</t>
+          <t>Prof. Dr. dr. Haerani Rasyid, Sp.PD, KGH, Sp.GK (K), M.Kes</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
@@ -1188,12 +1196,12 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>Dr. dr. Alfian Alfian Zainuddin, MKM</t>
+          <t>Prof. dr. Agussalim Bukhari, Sp.GK (K), Ph.D</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
@@ -1221,12 +1229,12 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>dr. St. Rabiul Zatalia, Sp.PD, KGH</t>
+          <t>Dr. dr. Alfian Alfian Zainuddin, MKM</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
@@ -1254,12 +1262,12 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>dr. Achmad Fikry, Sp.PD</t>
+          <t>dr. St. Rabiul Zatalia, Sp.PD, KGH</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D14" s="11" t="inlineStr">
@@ -1287,12 +1295,12 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>dr. Dedy Kusnadi, Sp.PD</t>
+          <t>dr. Achmad Fikry, Sp.PD</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D15" s="11" t="inlineStr">
@@ -1320,12 +1328,12 @@
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>dr. Idham Shadiq Kawu</t>
+          <t>dr. Dedy Kusnadi, Sp.PD</t>
         </is>
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D16" s="11" t="inlineStr">
@@ -1353,12 +1361,12 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>dr. Muhammad Arfandy</t>
+          <t>dr. Idham Shadiq Kawu</t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D17" s="11" t="inlineStr">
@@ -1384,10 +1392,26 @@
       <c r="A18" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="B18" s="12" t="n"/>
-      <c r="C18" s="12" t="n"/>
-      <c r="D18" s="12" t="n"/>
-      <c r="E18" s="11" t="n"/>
+      <c r="B18" s="11" t="inlineStr">
+        <is>
+          <t>dr. Muhammad Arfandy</t>
+        </is>
+      </c>
+      <c r="C18" s="11" t="inlineStr">
+        <is>
+          <t>Student</t>
+        </is>
+      </c>
+      <c r="D18" s="11" t="inlineStr">
+        <is>
+          <t>Hasanuddin University</t>
+        </is>
+      </c>
+      <c r="E18" s="11" t="inlineStr">
+        <is>
+          <t>Nephro &amp; nutriton research group is a study group that focus on nutrition management &amp; intervention in patients suffering from kidney disease, this group consists of nephrologist, clinical nutrition, epideniologist who focus on the field of nephrology and clinical nutrition. This group was formed to develop knowledge that can be useful in the management of therapy for patients suffering from kidney disease</t>
+        </is>
+      </c>
       <c r="F18" s="12" t="n"/>
       <c r="G18" s="12" t="n"/>
       <c r="H18" s="12" t="n"/>
@@ -1395,7 +1419,11 @@
       <c r="J18" s="12" t="n"/>
       <c r="K18" s="12" t="n"/>
       <c r="L18" s="12" t="n"/>
-      <c r="M18" s="12" t="n"/>
+      <c r="M18" s="11" t="inlineStr">
+        <is>
+          <t>Aktif</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
@@ -1584,15 +1612,32 @@
       <c r="L29" s="12" t="n"/>
       <c r="M29" s="12" t="n"/>
     </row>
+    <row r="30">
+      <c r="A30" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="B30" s="12" t="n"/>
+      <c r="C30" s="12" t="n"/>
+      <c r="D30" s="12" t="n"/>
+      <c r="E30" s="11" t="n"/>
+      <c r="F30" s="12" t="n"/>
+      <c r="G30" s="12" t="n"/>
+      <c r="H30" s="12" t="n"/>
+      <c r="I30" s="12" t="n"/>
+      <c r="J30" s="12" t="n"/>
+      <c r="K30" s="12" t="n"/>
+      <c r="L30" s="12" t="n"/>
+      <c r="M30" s="12" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:M2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="F5:H29" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F5:H30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$A$2:$A$39</formula1>
     </dataValidation>
-    <dataValidation sqref="M5:M29" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="M5:M30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$C$2:$C$3</formula1>
     </dataValidation>
   </dataValidations>
